--- a/data/processed/positivacao/2024-06_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-06_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26453,7 +26453,7 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr"/>
@@ -37493,7 +37493,7 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr"/>
@@ -65787,7 +65787,7 @@
     <row r="2519">
       <c r="A2519" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2519" t="inlineStr"/>
@@ -67380,12 +67380,12 @@
       <c r="A2581" t="inlineStr"/>
       <c r="B2581" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 13 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 13.419,84
+          <t>Vendedor 1 - VENDEDOR 01: positivou 13 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 13.419,84
 Vendedor 18 - LOJA: positivou 180 cliente(s), não positivou 717 cliente(s) - Total vendido: R$ 77.940,80
-Vendedor 3 - FERNANDA: positivou 93 cliente(s), não positivou 331 cliente(s) - Total vendido: R$ 162.420,68
-Vendedor 4 - DANIELA: positivou 90 cliente(s), não positivou 551 cliente(s) - Total vendido: R$ 47.616,82
+Vendedor 3 - VENDEDOR 03: positivou 93 cliente(s), não positivou 331 cliente(s) - Total vendido: R$ 162.420,68
+Vendedor 4 - VENDEDOR 04: positivou 90 cliente(s), não positivou 551 cliente(s) - Total vendido: R$ 47.616,82
 Vendedor 5 - SITE: positivou 4 cliente(s), não positivou 442 cliente(s) - Total vendido: R$ 1.348,37
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2581" t="inlineStr"/>
